--- a/lista_precios_clientes.xlsx
+++ b/lista_precios_clientes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M216"/>
+  <dimension ref="A1:M221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -793,15 +793,6 @@
       <c r="J16" s="8" t="n">
         <v>34260</v>
       </c>
-      <c r="K16" s="8" t="n">
-        <v>38100</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>41865</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>45700</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1012,11 +1003,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Superhéroes. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>22200</v>
+          <t>Pack x 10 Títeres de mano de Animalitos- Surtido a elección</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>49760</v>
       </c>
     </row>
     <row r="29">
@@ -1027,75 +1018,75 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Superhéroes. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>22200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Títeres Patrios. Títeres de Mano</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D30" s="8" t="n">
         <v>11450</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E30" s="8" t="n">
         <v>15250</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F30" s="8" t="n">
         <v>19100</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G30" s="8" t="n">
         <v>22850</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H30" s="8" t="n">
         <v>26650</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I30" s="8" t="n">
         <v>30950</v>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="J30" s="8" t="n">
         <v>34260</v>
       </c>
-      <c r="K29" s="8" t="n">
+      <c r="K30" s="8" t="n">
         <v>38100</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L30" s="8" t="n">
         <v>41865</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M30" s="8" t="n">
         <v>45700</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>el Gato y los cinco Ratoncitos Bailarines</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>22900</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>TEATROS CON TÍTERES</t>
         </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>37100</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>37100</v>
       </c>
     </row>
     <row r="33">
@@ -1106,11 +1097,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
+          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>30200</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="34">
@@ -1121,7 +1112,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
+          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -1136,26 +1127,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>34000</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>37100</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>42100</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>47100</v>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>52200</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>57200</v>
+          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="36">
@@ -1166,11 +1142,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
+          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>36800</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="37">
@@ -1181,7 +1157,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
+          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
@@ -1211,20 +1187,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>34000</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>37100</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>42100</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>47100</v>
+          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="39">
@@ -1235,7 +1202,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
         </is>
       </c>
       <c r="D39" s="8" t="n">
@@ -1250,6 +1217,12 @@
       <c r="G39" s="8" t="n">
         <v>47100</v>
       </c>
+      <c r="H39" s="8" t="n">
+        <v>52200</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>57200</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1259,14 +1232,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
-        </is>
+          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>37100</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>33400</v>
+        <v>42100</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>43420</v>
+        <v>47100</v>
       </c>
     </row>
     <row r="41">
@@ -1277,11 +1256,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>38650</v>
+          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>37100</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>42100</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>47100</v>
       </c>
     </row>
     <row r="42">
@@ -1292,38 +1280,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Teatro Granja con Títeres de La Granja</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>28500</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>30200</v>
+          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
+        </is>
       </c>
       <c r="F42" s="8" t="n">
         <v>33400</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>39950</v>
-      </c>
-      <c r="I42" s="8" t="n">
-        <v>43250</v>
-      </c>
-      <c r="J42" s="8" t="n">
-        <v>46500</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>49760</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>53025</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>56300</v>
+        <v>43420</v>
       </c>
     </row>
     <row r="43">
@@ -1334,17 +1298,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>28500</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>37100</v>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>42100</v>
+          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>38650</v>
       </c>
     </row>
     <row r="44">
@@ -1355,7 +1313,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
+          <t>Teatro Fondo del mar con Títeres del Océano</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
@@ -1373,6 +1331,12 @@
       <c r="H44" s="8" t="n">
         <v>39950</v>
       </c>
+      <c r="I44" s="8" t="n">
+        <v>43250</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>46500</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1382,7 +1346,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Teatro Selva con Títeres de la Selva Africana</t>
+          <t>Teatro Granja con Títeres de La Granja</t>
         </is>
       </c>
       <c r="D45" s="8" t="n">
@@ -1403,6 +1367,18 @@
       <c r="I45" s="8" t="n">
         <v>43250</v>
       </c>
+      <c r="J45" s="8" t="n">
+        <v>46500</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>53025</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>56300</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1412,11 +1388,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Teatro bosque con Títeres de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
+          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E46" s="8" t="n">
         <v>37100</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>42100</v>
       </c>
     </row>
     <row r="47">
@@ -1427,11 +1409,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>49900</v>
+          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>39950</v>
       </c>
     </row>
     <row r="48">
@@ -1442,11 +1436,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teatro ciudad con títeres de Superhéroes.</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>37100</v>
+          <t>Teatro Selva con Títeres de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>39950</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>43250</v>
       </c>
     </row>
     <row r="49">
@@ -1457,11 +1466,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+          <t>Teatro bosque con Títeres de Caperucita Roja</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>57800</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="50">
@@ -1472,38 +1481,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Teatro de la Época Colonial con Títeres Patrios</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>28500</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>30200</v>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>33400</v>
-      </c>
-      <c r="G50" s="8" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H50" s="8" t="n">
-        <v>39950</v>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>43250</v>
-      </c>
-      <c r="J50" s="8" t="n">
-        <v>46500</v>
-      </c>
-      <c r="K50" s="8" t="n">
-        <v>49760</v>
-      </c>
-      <c r="L50" s="8" t="n">
-        <v>53025</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>56300</v>
+          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>49900</v>
       </c>
     </row>
     <row r="51">
@@ -1514,75 +1496,102 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="n">
-        <v>28500</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>30200</v>
-      </c>
-      <c r="F51" s="8" t="n">
-        <v>33400</v>
-      </c>
-      <c r="G51" s="8" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H51" s="8" t="n">
-        <v>39950</v>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+          <t>Teatro ciudad con títeres de Superhéroes.</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>37100</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>57800</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>16300</v>
+          <t>Teatro de la Época Colonial con Títeres Patrios</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>39950</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>43250</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>46500</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>53025</v>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>56300</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>39950</v>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>18800</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>16300</v>
       </c>
     </row>
     <row r="56">
@@ -1593,7 +1602,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
+          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
@@ -1608,11 +1617,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>18000</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="58">
@@ -1623,11 +1632,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>18800</v>
+        <v>16300</v>
       </c>
     </row>
     <row r="59">
@@ -1638,20 +1647,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>18800</v>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>21250</v>
-      </c>
-      <c r="G59" s="8" t="n">
-        <v>23670</v>
-      </c>
-      <c r="H59" s="8" t="n">
-        <v>26100</v>
+          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="60">
@@ -1662,11 +1662,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>18800</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="61">
@@ -1677,20 +1677,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>18150</v>
-      </c>
-      <c r="G61" s="8" t="n">
-        <v>19920</v>
-      </c>
-      <c r="H61" s="8" t="n">
-        <v>21800</v>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>23550</v>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="62">
@@ -1701,20 +1692,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
         </is>
       </c>
       <c r="E62" s="8" t="n">
-        <v>16300</v>
+        <v>18800</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>18150</v>
+        <v>21250</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>19920</v>
+        <v>23670</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>21800</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="63">
@@ -1725,7 +1716,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
+          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
         </is>
       </c>
       <c r="C63" s="7" t="n">
@@ -1740,11 +1731,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>19980</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="65">
@@ -1755,17 +1755,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>14500</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
+        </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>16200</v>
+        <v>16300</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>19360</v>
+        <v>18150</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>21800</v>
       </c>
     </row>
     <row r="66">
@@ -1776,23 +1779,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>16300</v>
-      </c>
-      <c r="F66" s="8" t="n">
-        <v>18150</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>19920</v>
-      </c>
-      <c r="H66" s="8" t="n">
-        <v>21800</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>23550</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="67">
@@ -1803,11 +1794,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="n">
-        <v>19950</v>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de Animalitos marinos</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>23550</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>25350</v>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="68">
@@ -1818,29 +1827,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>16300</v>
-      </c>
-      <c r="F68" s="8" t="n">
-        <v>18150</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>19920</v>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>21800</v>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>23550</v>
-      </c>
-      <c r="J68" s="8" t="n">
-        <v>25350</v>
-      </c>
-      <c r="K68" s="8" t="n">
-        <v>27200</v>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>19980</v>
       </c>
     </row>
     <row r="69">
@@ -1851,11 +1842,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="n">
-        <v>18200</v>
+          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>16200</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>19360</v>
       </c>
     </row>
     <row r="70">
@@ -1866,11 +1863,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n">
-        <v>18000</v>
+          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="71">
@@ -1881,20 +1890,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Animalitos domésticos</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>7800</v>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H71" s="8" t="n">
-        <v>13200</v>
+          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>19950</v>
       </c>
     </row>
     <row r="72">
@@ -1905,11 +1905,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Caperucita roja</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="n">
-        <v>7800</v>
+          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>23550</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>25350</v>
+      </c>
+      <c r="K72" s="8" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="73">
@@ -1920,11 +1938,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>10300</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="74">
@@ -1935,11 +1953,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento de Hadas</t>
+          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>10300</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="75">
@@ -1950,11 +1968,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Títeres de dedo de El Circo Mágico</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Animalitos del Mar</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="76">
@@ -1965,17 +1995,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Heroínas de cuento</t>
+          <t>Títeres de dedo de Animalitos domésticos</t>
         </is>
       </c>
       <c r="E76" s="8" t="n">
-        <v>10300</v>
+        <v>7800</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>12700</v>
+        <v>9600</v>
+      </c>
+      <c r="G76" s="8" t="n">
+        <v>11400</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>17600</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="77">
@@ -1986,20 +2019,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Familia Monte Espino</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="n">
+          <t>Títeres de dedo de Caperucita roja</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n">
         <v>7800</v>
-      </c>
-      <c r="F77" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G77" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H77" s="8" t="n">
-        <v>13200</v>
       </c>
     </row>
     <row r="78">
@@ -2010,11 +2034,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Prehistoria</t>
+          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="C78" s="7" t="n">
-        <v>10825</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="79">
@@ -2025,11 +2049,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Sirenita</t>
+          <t>Títeres de dedo de Cuento de Hadas</t>
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>11450</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="80">
@@ -2040,20 +2064,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>7800</v>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G80" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H80" s="8" t="n">
-        <v>13200</v>
+          <t>Títeres de dedo de El Circo Mágico</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="81">
@@ -2064,11 +2079,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Piratas Siete Mares</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="n">
-        <v>7800</v>
+          <t>Títeres de dedo de Heroínas de cuento</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>10300</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>12700</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>17600</v>
       </c>
     </row>
     <row r="82">
@@ -2079,11 +2100,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="n">
+          <t>Títeres de dedo de La Familia Monte Espino</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="n">
         <v>7800</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="83">
@@ -2094,23 +2124,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Africana</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>7800</v>
-      </c>
-      <c r="F83" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G83" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H83" s="8" t="n">
-        <v>13200</v>
-      </c>
-      <c r="I83" s="8" t="n">
-        <v>15100</v>
+          <t>Títeres de dedo de La Prehistoria</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>10825</v>
       </c>
     </row>
     <row r="84">
@@ -2121,14 +2139,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Misionera</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>7800</v>
-      </c>
-      <c r="F84" s="8" t="n">
-        <v>9600</v>
+          <t>Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>11450</v>
       </c>
     </row>
     <row r="85">
@@ -2139,11 +2154,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Superhéroes</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G85" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="86">
@@ -2154,23 +2178,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Títeres de dedo de granja</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="n">
+          <t>Títeres de dedo de Los Piratas Siete Mares</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="n">
         <v>7800</v>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G86" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H86" s="8" t="n">
-        <v>13200</v>
-      </c>
-      <c r="I86" s="8" t="n">
-        <v>15100</v>
       </c>
     </row>
     <row r="87">
@@ -2181,93 +2193,120 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>10300</v>
-      </c>
-    </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Títeres de dedo de Selva Africana</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I88" s="8" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Elefante</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="n">
-        <v>12000</v>
+          <t>Títeres de dedo de Selva Misionera</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>9600</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Espacio</t>
+          <t>Títeres de dedo de Superhéroes</t>
         </is>
       </c>
       <c r="C90" s="7" t="n">
-        <v>12000</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Gato automovilista</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="n">
-        <v>12000</v>
+          <t>Títeres de dedo de granja</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I91" s="8" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Bolsito Amasando ideas Pajaritos</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Valija de Arte Mini Artista, Dinosaurios</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="n">
-        <v>19500</v>
       </c>
     </row>
     <row r="94">
@@ -2278,11 +2317,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Haditas</t>
+          <t>Bolsito Amasando ideas Elefante</t>
         </is>
       </c>
       <c r="C94" s="7" t="n">
-        <v>19500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="95">
@@ -2293,11 +2332,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Piratas</t>
+          <t>Bolsito Amasando ideas Espacio</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>19500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="96">
@@ -2308,11 +2347,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Ponis</t>
+          <t>Bolsito Amasando ideas Gato automovilista</t>
         </is>
       </c>
       <c r="C96" s="7" t="n">
-        <v>19500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="97">
@@ -2323,11 +2362,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Sirenitas</t>
+          <t>Bolsito Amasando ideas Pajaritos</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>19500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="98">
@@ -2338,7 +2377,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Superhéroes</t>
+          <t>Valija de Arte Mini Artista, Dinosaurios</t>
         </is>
       </c>
       <c r="C98" s="7" t="n">
@@ -2353,11 +2392,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Astronautas</t>
+          <t>Valija de Arte Mini Artista, Haditas</t>
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>25850</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="100">
@@ -2368,11 +2407,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
+          <t>Valija de Arte Mini Artista, Piratas</t>
         </is>
       </c>
       <c r="C100" s="7" t="n">
-        <v>25850</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="101">
@@ -2383,11 +2422,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
+          <t>Valija de Arte Mini Artista, Ponis</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>25850</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="102">
@@ -2398,11 +2437,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Monstruos</t>
+          <t>Valija de Arte Mini Artista, Sirenitas</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>25850</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="103">
@@ -2413,11 +2452,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+          <t>Valija de Arte Mini Artista, Superhéroes</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>25850</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="104">
@@ -2428,7 +2467,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
+          <t>Valija de Arte Mis Diseños. Astronautas</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
@@ -2443,7 +2482,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Princesa</t>
+          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
@@ -2458,7 +2497,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Robots</t>
+          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
@@ -2473,93 +2512,93 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Unicornio</t>
+          <t>Valija de Arte Mis Diseños. Monstruos</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bolsito Chef nena</t>
+          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>11500</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bolsito Chef varón</t>
+          <t>Valija de Arte Mis Diseños. Princesa</t>
         </is>
       </c>
       <c r="C110" s="7" t="n">
-        <v>11500</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bolsito Explorador Jirafas</t>
+          <t>Valija de Arte Mis Diseños. Robots</t>
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>11500</v>
+        <v>25850</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Valija de Arte Mis Diseños. Unicornio</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>25850</v>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Bolsito Explorador África</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="n">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Bolsito Mini Peluquería</t>
-        </is>
-      </c>
-      <c r="C113" s="7" t="n">
-        <v>11500</v>
       </c>
     </row>
     <row r="114">
@@ -2570,11 +2609,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+          <t>Bolsito Chef nena</t>
         </is>
       </c>
       <c r="C114" s="7" t="n">
-        <v>16500</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="115">
@@ -2585,11 +2624,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef nena</t>
+          <t>Bolsito Chef varón</t>
         </is>
       </c>
       <c r="C115" s="7" t="n">
-        <v>21000</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="116">
@@ -2600,11 +2639,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef varón</t>
+          <t>Bolsito Explorador Jirafas</t>
         </is>
       </c>
       <c r="C116" s="7" t="n">
-        <v>21000</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="117">
@@ -2615,11 +2654,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Valija de Mini Doctor</t>
+          <t>Bolsito Explorador África</t>
         </is>
       </c>
       <c r="C117" s="7" t="n">
-        <v>37500</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="118">
@@ -2630,11 +2669,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Valija de Mini Exploradores</t>
+          <t>Bolsito Mini Peluquería</t>
         </is>
       </c>
       <c r="C118" s="7" t="n">
-        <v>24800</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="119">
@@ -2645,11 +2684,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Valija de Mini Jardineros</t>
+          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>23500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="120">
@@ -2660,11 +2699,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestra</t>
+          <t>Valija de Mini Chef nena</t>
         </is>
       </c>
       <c r="C120" s="7" t="n">
-        <v>28600</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="121">
@@ -2675,11 +2714,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestro</t>
+          <t>Valija de Mini Chef varón</t>
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>28600</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="122">
@@ -2690,11 +2729,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Valija de Mini Spa</t>
+          <t>Valija de Mini Doctor</t>
         </is>
       </c>
       <c r="C122" s="7" t="n">
-        <v>29800</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="123">
@@ -2705,11 +2744,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Valija de Mini Veterinarios</t>
+          <t>Valija de Mini Exploradores</t>
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>26400</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="124">
@@ -2720,11 +2759,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Valija de Tarde de Mate</t>
+          <t>Valija de Mini Jardineros</t>
         </is>
       </c>
       <c r="C124" s="7" t="n">
-        <v>19500</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="125">
@@ -2735,93 +2774,93 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Valija de Tardes de Té</t>
+          <t>Valija de Mini Maestra</t>
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="126" ht="28" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
+        <v>28600</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Valija de Mini Maestro</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Disfraz de Anna (Frozen)</t>
+          <t>Valija de Mini Spa</t>
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>24850</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Disfraz de Bella</t>
+          <t>Valija de Mini Veterinarios</t>
         </is>
       </c>
       <c r="C128" s="7" t="n">
-        <v>23970</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Disfraz de Blancanieves</t>
+          <t>Valija de Tarde de Mate</t>
         </is>
       </c>
       <c r="C129" s="7" t="n">
-        <v>24850</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Valija de Tardes de Té</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENAS</t>
         </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Disfraz de Cenicienta</t>
-        </is>
-      </c>
-      <c r="C130" s="7" t="n">
-        <v>23970</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Disfraz de Elsa (Frozen)</t>
-        </is>
-      </c>
-      <c r="C131" s="7" t="n">
-        <v>24850</v>
       </c>
     </row>
     <row r="132">
@@ -2832,11 +2871,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Disfraz de Mira K-Pop Demon Hunters</t>
+          <t>Disfraz de Anna (Frozen)</t>
         </is>
       </c>
       <c r="C132" s="7" t="n">
-        <v>38500</v>
+        <v>24850</v>
       </c>
     </row>
     <row r="133">
@@ -2847,11 +2886,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Disfraz de Moana</t>
+          <t>Disfraz de Bella</t>
         </is>
       </c>
       <c r="C133" s="7" t="n">
-        <v>24500</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="134">
@@ -2862,11 +2901,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Disfraz de Mujer Maravilla</t>
+          <t>Disfraz de Blancanieves</t>
         </is>
       </c>
       <c r="C134" s="7" t="n">
-        <v>19850</v>
+        <v>24850</v>
       </c>
     </row>
     <row r="135">
@@ -2877,7 +2916,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
+          <t>Disfraz de Cenicienta</t>
         </is>
       </c>
       <c r="C135" s="7" t="n">
@@ -2892,11 +2931,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Disfraz de Rapunzel Encantada</t>
+          <t>Disfraz de Elsa (Frozen)</t>
         </is>
       </c>
       <c r="C136" s="7" t="n">
-        <v>33300</v>
+        <v>24850</v>
       </c>
     </row>
     <row r="137">
@@ -2907,11 +2946,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
+          <t>Disfraz de Mira K-Pop Demon Hunters</t>
         </is>
       </c>
       <c r="C137" s="7" t="n">
-        <v>28500</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="138">
@@ -2922,11 +2961,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
+          <t>Disfraz de Moana</t>
         </is>
       </c>
       <c r="C138" s="7" t="n">
-        <v>51800</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="139">
@@ -2937,11 +2976,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
+          <t>Disfraz de Mujer Maravilla</t>
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>53200</v>
+        <v>19850</v>
       </c>
     </row>
     <row r="140">
@@ -2952,11 +2991,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Disfraz de Sirenita</t>
+          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
         </is>
       </c>
       <c r="C140" s="7" t="n">
-        <v>22500</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="141">
@@ -2967,11 +3006,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Disfraz de Unicornio Mágico</t>
+          <t>Disfraz de Rapunzel Encantada</t>
         </is>
       </c>
       <c r="C141" s="7" t="n">
-        <v>27400</v>
+        <v>33300</v>
       </c>
     </row>
     <row r="142">
@@ -2982,11 +3021,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
+          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
         </is>
       </c>
       <c r="C142" s="7" t="n">
-        <v>45000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="143">
@@ -2997,11 +3036,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tutú de Bailarina Unicornio</t>
+          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>23200</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="144">
@@ -3012,93 +3051,93 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tutú de bailarina</t>
+          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
         </is>
       </c>
       <c r="C144" s="7" t="n">
-        <v>19500</v>
-      </c>
-    </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
+        <v>53200</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Disfraz de Sirenita</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>22500</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENES</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Disfraz de Batman</t>
+          <t>Disfraz de Unicornio Mágico</t>
         </is>
       </c>
       <c r="C146" s="7" t="n">
-        <v>23500</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENES</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Disfraz de Bombero</t>
+          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>15000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENES</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Disfraz de Capitán América</t>
+          <t>Tutú de Bailarina Unicornio</t>
         </is>
       </c>
       <c r="C148" s="7" t="n">
-        <v>23500</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Tutú de bailarina</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="150" ht="28" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENES</t>
         </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Disfraz de Hombre Araña</t>
-        </is>
-      </c>
-      <c r="C149" s="7" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Disfraz de Pirata</t>
-        </is>
-      </c>
-      <c r="C150" s="7" t="n">
-        <v>18000</v>
       </c>
     </row>
     <row r="151">
@@ -3109,11 +3148,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Disfraz de Policía</t>
+          <t>Disfraz de Batman</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
-        <v>15000</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="152">
@@ -3124,111 +3163,119 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Disfraz de Superman</t>
+          <t>Disfraz de Bombero</t>
         </is>
       </c>
       <c r="C152" s="7" t="n">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="153" ht="28" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>DISFRACES DE ANIMALITOS</t>
-        </is>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Disfraz de Capitán América</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DISFRACES DE ANIMALITOS</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
+          <t>Disfraz de Hombre Araña</t>
         </is>
       </c>
       <c r="C154" s="7" t="n">
-        <v>23500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DISFRACES DE ANIMALITOS</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Disfraz de Cebra</t>
+          <t>Disfraz de Pirata</t>
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>23500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DISFRACES DE ANIMALITOS</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Disfraz de Dinosaurio</t>
+          <t>Disfraz de Policía</t>
         </is>
       </c>
       <c r="C156" s="7" t="n">
-        <v>25200</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DISFRACES DE ANIMALITOS</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Disfraz de Tigre</t>
+          <t>Disfraz de Superman</t>
         </is>
       </c>
       <c r="C157" s="7" t="n">
-        <v>23500</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
+          <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
+          <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Caramelera Calabaza</t>
+          <t>Disfraz de Araña</t>
         </is>
       </c>
       <c r="C159" s="7" t="n">
-        <v>9000</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
+          <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
+          <t>Disfraz de Cebra</t>
         </is>
       </c>
       <c r="C160" s="7" t="n">
@@ -3238,46 +3285,38 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
+          <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Fuxia</t>
+          <t>Disfraz de Dinosaurio</t>
         </is>
       </c>
       <c r="C161" s="7" t="n">
-        <v>25500</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Disfraz de Tigre</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="n">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="163" ht="28" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
           <t>DISFRACES DE HALLOWEEN</t>
         </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Disfraz de Brujita Naranja</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="n">
-        <v>25500</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Disfraz de Brujita Verde</t>
-        </is>
-      </c>
-      <c r="C163" s="7" t="n">
-        <v>25500</v>
       </c>
     </row>
     <row r="164">
@@ -3288,11 +3327,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Violeta</t>
+          <t>Caramelera Calabaza</t>
         </is>
       </c>
       <c r="C164" s="7" t="n">
-        <v>25500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="165">
@@ -3303,7 +3342,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Disfraz de Calabaza</t>
+          <t>Disfraz de Araña</t>
         </is>
       </c>
       <c r="C165" s="7" t="n">
@@ -3318,11 +3357,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Disfraz de Esqueleto</t>
+          <t>Disfraz de Brujita Fuxia</t>
         </is>
       </c>
       <c r="C166" s="7" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="167">
@@ -3333,11 +3372,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Disfraz de Merlina</t>
+          <t>Disfraz de Brujita Naranja</t>
         </is>
       </c>
       <c r="C167" s="7" t="n">
-        <v>32000</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="168">
@@ -3348,93 +3387,93 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Disfraz de Vampira</t>
+          <t>Disfraz de Brujita Verde</t>
         </is>
       </c>
       <c r="C168" s="7" t="n">
-        <v>25300</v>
-      </c>
-    </row>
-    <row r="169" ht="28" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Disfraz de Brujita Violeta</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cactus</t>
+          <t>Disfraz de Calabaza</t>
         </is>
       </c>
       <c r="C170" s="7" t="n">
-        <v>22900</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cebra y Jirafa</t>
+          <t>Disfraz de Esqueleto</t>
         </is>
       </c>
       <c r="C171" s="7" t="n">
-        <v>22900</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Gatitos</t>
+          <t>Disfraz de Merlina</t>
         </is>
       </c>
       <c r="C172" s="7" t="n">
-        <v>22900</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Disfraz de Vampira</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="n">
+        <v>25300</v>
+      </c>
+    </row>
+    <row r="174" ht="28" customHeight="1">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
           <t>JUGUETES PARA BEBÉS</t>
         </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Cesto para juguetes Indi</t>
-        </is>
-      </c>
-      <c r="C173" s="7" t="n">
-        <v>22900</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Globo Pelota Animalitos</t>
-        </is>
-      </c>
-      <c r="C174" s="7" t="n">
-        <v>6800</v>
       </c>
     </row>
     <row r="175">
@@ -3445,11 +3484,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Globo Pelota Dinosaurios</t>
+          <t>Cesto para juguetes Cactus</t>
         </is>
       </c>
       <c r="C175" s="7" t="n">
-        <v>6800</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="176">
@@ -3460,11 +3499,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Globo Pelota Gatitos</t>
+          <t>Cesto para juguetes Cebra y Jirafa</t>
         </is>
       </c>
       <c r="C176" s="7" t="n">
-        <v>6800</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="177">
@@ -3475,11 +3514,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Globo Pelota Haditas</t>
+          <t>Cesto para juguetes Gatitos</t>
         </is>
       </c>
       <c r="C177" s="7" t="n">
-        <v>6800</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="178">
@@ -3490,11 +3529,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Globo Pelota Monstruos</t>
+          <t>Cesto para juguetes Indi</t>
         </is>
       </c>
       <c r="C178" s="7" t="n">
-        <v>6800</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="179">
@@ -3505,7 +3544,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Globo Pelota Selva</t>
+          <t>Globo Pelota Animalitos</t>
         </is>
       </c>
       <c r="C179" s="7" t="n">
@@ -3520,11 +3559,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Libro para bebé "Coral"</t>
+          <t>Globo Pelota Dinosaurios</t>
         </is>
       </c>
       <c r="C180" s="7" t="n">
-        <v>8400</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="181">
@@ -3535,11 +3574,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Libro para bebé "Cosquillitas"</t>
+          <t>Globo Pelota Gatitos</t>
         </is>
       </c>
       <c r="C181" s="7" t="n">
-        <v>8400</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="182">
@@ -3550,11 +3589,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Libro para bebé "Mariposas"</t>
+          <t>Globo Pelota Haditas</t>
         </is>
       </c>
       <c r="C182" s="7" t="n">
-        <v>8400</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="183">
@@ -3565,11 +3604,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Manta para bebé "Animalitos de la Selva"</t>
+          <t>Globo Pelota Monstruos</t>
         </is>
       </c>
       <c r="C183" s="7" t="n">
-        <v>15600</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="184">
@@ -3580,11 +3619,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Manta para bebé "La Ciudad"</t>
+          <t>Globo Pelota Selva</t>
         </is>
       </c>
       <c r="C184" s="7" t="n">
-        <v>15600</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="185">
@@ -3595,11 +3634,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Manta para bebé "Mininos"</t>
+          <t>Libro para bebé "Coral"</t>
         </is>
       </c>
       <c r="C185" s="7" t="n">
-        <v>15600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="186">
@@ -3610,11 +3649,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Animalitos</t>
+          <t>Libro para bebé "Cosquillitas"</t>
         </is>
       </c>
       <c r="C186" s="7" t="n">
-        <v>15950</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="187">
@@ -3625,11 +3664,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Dinosaurios</t>
+          <t>Libro para bebé "Mariposas"</t>
         </is>
       </c>
       <c r="C187" s="7" t="n">
-        <v>15950</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="188">
@@ -3640,11 +3679,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Gatitos</t>
+          <t>Manta para bebé "Animalitos de la Selva"</t>
         </is>
       </c>
       <c r="C188" s="7" t="n">
-        <v>15950</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="189">
@@ -3655,11 +3694,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Selva</t>
+          <t>Manta para bebé "La Ciudad"</t>
         </is>
       </c>
       <c r="C189" s="7" t="n">
-        <v>15950</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="190">
@@ -3670,11 +3709,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
+          <t>Manta para bebé "Mininos"</t>
         </is>
       </c>
       <c r="C190" s="7" t="n">
-        <v>7500</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="191">
@@ -3685,93 +3724,93 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Rayuela de tela para aprender los números jugando</t>
+          <t>Pelota de Trapo  Animalitos</t>
         </is>
       </c>
       <c r="C191" s="7" t="n">
-        <v>24500</v>
-      </c>
-    </row>
-    <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
+        <v>15950</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Pelota de Trapo  Dinosaurios</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Aurora</t>
+          <t>Pelota de Trapo Gatitos</t>
         </is>
       </c>
       <c r="C193" s="7" t="n">
-        <v>24350</v>
+        <v>15950</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Bella</t>
+          <t>Pelota de Trapo Selva</t>
         </is>
       </c>
       <c r="C194" s="7" t="n">
-        <v>24350</v>
+        <v>15950</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Blancanieves</t>
+          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
         </is>
       </c>
       <c r="C195" s="7" t="n">
-        <v>24350</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Rayuela de tela para aprender los números jugando</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="n">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="197" ht="28" customHeight="1">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
           <t>MUÑECAS DE TRAPO</t>
         </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Muñeca Piccolina Cenicienta</t>
-        </is>
-      </c>
-      <c r="C196" s="7" t="n">
-        <v>24350</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Muñeca Piccolina Coqueta</t>
-        </is>
-      </c>
-      <c r="C197" s="7" t="n">
-        <v>24350</v>
       </c>
     </row>
     <row r="198">
@@ -3782,7 +3821,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Deportiva</t>
+          <t>Muñeca Piccolina Aurora</t>
         </is>
       </c>
       <c r="C198" s="7" t="n">
@@ -3797,7 +3836,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Folk</t>
+          <t>Muñeca Piccolina Bella</t>
         </is>
       </c>
       <c r="C199" s="7" t="n">
@@ -3812,7 +3851,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Jardinera</t>
+          <t>Muñeca Piccolina Blancanieves</t>
         </is>
       </c>
       <c r="C200" s="7" t="n">
@@ -3827,7 +3866,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Rapunsel</t>
+          <t>Muñeca Piccolina Cenicienta</t>
         </is>
       </c>
       <c r="C201" s="7" t="n">
@@ -3842,7 +3881,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Romántica</t>
+          <t>Muñeca Piccolina Coqueta</t>
         </is>
       </c>
       <c r="C202" s="7" t="n">
@@ -3857,7 +3896,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Sofía</t>
+          <t>Muñeca Piccolina Deportiva</t>
         </is>
       </c>
       <c r="C203" s="7" t="n">
@@ -3872,7 +3911,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina doctora</t>
+          <t>Muñeca Piccolina Folk</t>
         </is>
       </c>
       <c r="C204" s="7" t="n">
@@ -3887,11 +3926,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Traje de doctora para muñecas</t>
+          <t>Muñeca Piccolina Jardinera</t>
         </is>
       </c>
       <c r="C205" s="7" t="n">
-        <v>8300</v>
+        <v>24350</v>
       </c>
     </row>
     <row r="206">
@@ -3902,11 +3941,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Traje de jardinera para muñecas</t>
+          <t>Muñeca Piccolina Rapunsel</t>
         </is>
       </c>
       <c r="C206" s="7" t="n">
-        <v>8300</v>
+        <v>24350</v>
       </c>
     </row>
     <row r="207">
@@ -3917,11 +3956,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Traje deportivo para muñecas</t>
+          <t>Muñeca Piccolina Romántica</t>
         </is>
       </c>
       <c r="C207" s="7" t="n">
-        <v>8300</v>
+        <v>24350</v>
       </c>
     </row>
     <row r="208">
@@ -3932,11 +3971,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Vestido campesino para muñecas</t>
+          <t>Muñeca Piccolina Sofía</t>
         </is>
       </c>
       <c r="C208" s="7" t="n">
-        <v>8300</v>
+        <v>24350</v>
       </c>
     </row>
     <row r="209">
@@ -3947,11 +3986,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Vestido coqueta para muñecas</t>
+          <t>Muñeca Piccolina doctora</t>
         </is>
       </c>
       <c r="C209" s="7" t="n">
-        <v>8300</v>
+        <v>24350</v>
       </c>
     </row>
     <row r="210">
@@ -3962,7 +4001,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Vestido de Aurora para muñecas</t>
+          <t>Traje de doctora para muñecas</t>
         </is>
       </c>
       <c r="C210" s="7" t="n">
@@ -3977,7 +4016,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Vestido de Bella para muñecas</t>
+          <t>Traje de jardinera para muñecas</t>
         </is>
       </c>
       <c r="C211" s="7" t="n">
@@ -3992,7 +4031,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Vestido de Blancanieves para muñecas</t>
+          <t>Traje deportivo para muñecas</t>
         </is>
       </c>
       <c r="C212" s="7" t="n">
@@ -4007,7 +4046,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Vestido de Cenicienta para muñecas</t>
+          <t>Vestido campesino para muñecas</t>
         </is>
       </c>
       <c r="C213" s="7" t="n">
@@ -4022,7 +4061,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Vestido de Princesa Sofía para muñecas</t>
+          <t>Vestido coqueta para muñecas</t>
         </is>
       </c>
       <c r="C214" s="7" t="n">
@@ -4037,7 +4076,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vestido de Rapunzel para muñecas</t>
+          <t>Vestido de Aurora para muñecas</t>
         </is>
       </c>
       <c r="C215" s="7" t="n">
@@ -4052,29 +4091,104 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
+          <t>Vestido de Bella para muñecas</t>
+        </is>
+      </c>
+      <c r="C216" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Vestido de Blancanieves para muñecas</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Vestido de Cenicienta para muñecas</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Vestido de Princesa Sofía para muñecas</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Vestido de Rapunzel para muñecas</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
           <t>Vestido romántico para muñecas</t>
         </is>
       </c>
-      <c r="C216" s="7" t="n">
+      <c r="C221" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A108:M108"/>
+    <mergeCell ref="A174:M174"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A169:M169"/>
-    <mergeCell ref="A126:M126"/>
+    <mergeCell ref="A150:M150"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A93:M93"/>
     <mergeCell ref="A158:M158"/>
+    <mergeCell ref="A197:M197"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A88:M88"/>
-    <mergeCell ref="A145:M145"/>
-    <mergeCell ref="A153:M153"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="A192:M192"/>
+    <mergeCell ref="A131:M131"/>
+    <mergeCell ref="A163:M163"/>
+    <mergeCell ref="A55:M55"/>
     <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="A113:M113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lista_precios_clientes.xlsx
+++ b/lista_precios_clientes.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M221"/>
+  <dimension ref="A1:M222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -970,17 +970,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
-        </is>
+          <t>Mis amigos del Celeste Océano</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>11450</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>15250</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>19100</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>24575</v>
+        <v>22850</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>30120</v>
+        <v>26650</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>30950</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>34260</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>38100</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>41865</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>45700</v>
       </c>
     </row>
     <row r="27">
@@ -991,8 +1012,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Navidad. Títeres de Mano.</t>
-        </is>
+          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>19100</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>24575</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>30120</v>
       </c>
     </row>
     <row r="28">
@@ -1003,11 +1033,8 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pack x 10 Títeres de mano de Animalitos- Surtido a elección</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>49760</v>
+          <t>Navidad. Títeres de Mano.</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1018,11 +1045,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Superhéroes. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>22200</v>
+          <t>Pack x 10 Títeres de mano de Animalitos- Surtido a elección</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>49760</v>
       </c>
     </row>
     <row r="30">
@@ -1033,38 +1060,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Títeres Patrios. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>11450</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>15250</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>19100</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>22850</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>26650</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>30950</v>
-      </c>
-      <c r="J30" s="8" t="n">
-        <v>34260</v>
-      </c>
-      <c r="K30" s="8" t="n">
-        <v>38100</v>
-      </c>
-      <c r="L30" s="8" t="n">
-        <v>41865</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>45700</v>
+          <t>Superhéroes. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>22200</v>
       </c>
     </row>
     <row r="31">
@@ -1075,33 +1075,60 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Títeres Patrios. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>11450</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>15250</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>19100</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>22850</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>26650</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>30950</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>34260</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>38100</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>41865</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>el Gato y los cinco Ratoncitos Bailarines</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C32" s="7" t="n">
         <v>22900</v>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>TEATROS CON TÍTERES</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>37100</v>
       </c>
     </row>
     <row r="34">
@@ -1112,7 +1139,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
+          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -1127,11 +1154,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
+          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>30200</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="36">
@@ -1142,11 +1169,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
+          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>37100</v>
+        <v>30200</v>
       </c>
     </row>
     <row r="37">
@@ -1157,26 +1184,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>34000</v>
-      </c>
-      <c r="E37" s="8" t="n">
+          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
         <v>37100</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>42100</v>
-      </c>
-      <c r="G37" s="8" t="n">
-        <v>47100</v>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>52200</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>57200</v>
       </c>
     </row>
     <row r="38">
@@ -1187,11 +1199,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>36800</v>
+          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>37100</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>42100</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>47100</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>52200</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>57200</v>
       </c>
     </row>
     <row r="39">
@@ -1202,26 +1229,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>34000</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>37100</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>42100</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>47100</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>52200</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>57200</v>
+          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="40">
@@ -1232,7 +1244,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
+          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
@@ -1247,6 +1259,12 @@
       <c r="G40" s="8" t="n">
         <v>47100</v>
       </c>
+      <c r="H40" s="8" t="n">
+        <v>52200</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>57200</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1256,7 +1274,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
         </is>
       </c>
       <c r="D41" s="8" t="n">
@@ -1280,14 +1298,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
-        </is>
+          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>37100</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>33400</v>
+        <v>42100</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>43420</v>
+        <v>47100</v>
       </c>
     </row>
     <row r="43">
@@ -1298,11 +1322,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="n">
-        <v>38650</v>
+          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>43420</v>
       </c>
     </row>
     <row r="44">
@@ -1313,29 +1340,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Teatro Fondo del mar con Títeres del Océano</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>28500</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>30200</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>33400</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>39950</v>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>43250</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>46500</v>
+          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>38650</v>
       </c>
     </row>
     <row r="45">
@@ -1346,7 +1355,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Teatro Granja con Títeres de La Granja</t>
+          <t>Teatro Fondo del mar con Títeres del Océano</t>
         </is>
       </c>
       <c r="D45" s="8" t="n">
@@ -1370,15 +1379,6 @@
       <c r="J45" s="8" t="n">
         <v>46500</v>
       </c>
-      <c r="K45" s="8" t="n">
-        <v>49760</v>
-      </c>
-      <c r="L45" s="8" t="n">
-        <v>53025</v>
-      </c>
-      <c r="M45" s="8" t="n">
-        <v>56300</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1388,17 +1388,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
+          <t>Teatro Granja con Títeres de La Granja</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
         <v>28500</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>37100</v>
+        <v>30200</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>42100</v>
+        <v>33400</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>39950</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>43250</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>46500</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>53025</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>56300</v>
       </c>
     </row>
     <row r="47">
@@ -1409,23 +1430,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
+          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
         </is>
       </c>
       <c r="D47" s="8" t="n">
         <v>28500</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>30200</v>
+        <v>37100</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>33400</v>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H47" s="8" t="n">
-        <v>39950</v>
+        <v>42100</v>
       </c>
     </row>
     <row r="48">
@@ -1436,7 +1451,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teatro Selva con Títeres de la Selva Africana</t>
+          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
@@ -1454,9 +1469,6 @@
       <c r="H48" s="8" t="n">
         <v>39950</v>
       </c>
-      <c r="I48" s="8" t="n">
-        <v>43250</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1466,11 +1478,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Teatro bosque con Títeres de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>37100</v>
+          <t>Teatro Selva con Títeres de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>39950</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>43250</v>
       </c>
     </row>
     <row r="50">
@@ -1481,11 +1508,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
+          <t>Teatro bosque con Títeres de Caperucita Roja</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>49900</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="51">
@@ -1496,11 +1523,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Teatro ciudad con títeres de Superhéroes.</t>
+          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>37100</v>
+        <v>49900</v>
       </c>
     </row>
     <row r="52">
@@ -1511,11 +1538,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+          <t>Teatro ciudad con títeres de Superhéroes.</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>57800</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="53">
@@ -1526,38 +1553,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Teatro de la Época Colonial con Títeres Patrios</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="n">
-        <v>28500</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>30200</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>33400</v>
-      </c>
-      <c r="G53" s="8" t="n">
-        <v>36700</v>
-      </c>
-      <c r="H53" s="8" t="n">
-        <v>39950</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>43250</v>
-      </c>
-      <c r="J53" s="8" t="n">
-        <v>46500</v>
-      </c>
-      <c r="K53" s="8" t="n">
-        <v>49760</v>
-      </c>
-      <c r="L53" s="8" t="n">
-        <v>53025</v>
-      </c>
-      <c r="M53" s="8" t="n">
-        <v>56300</v>
+          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>57800</v>
       </c>
     </row>
     <row r="54">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
+          <t>Teatro de la Época Colonial con Títeres Patrios</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
@@ -1586,27 +1586,54 @@
       <c r="H54" s="8" t="n">
         <v>39950</v>
       </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="I54" s="8" t="n">
+        <v>43250</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>46500</v>
+      </c>
+      <c r="K54" s="8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>53025</v>
+      </c>
+      <c r="M54" s="8" t="n">
+        <v>56300</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>36700</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>39950</v>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>16300</v>
       </c>
     </row>
     <row r="57">
@@ -1617,11 +1644,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
+          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>18800</v>
+        <v>16300</v>
       </c>
     </row>
     <row r="58">
@@ -1632,11 +1659,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>16300</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="59">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
@@ -1662,11 +1689,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>18000</v>
+        <v>16300</v>
       </c>
     </row>
     <row r="61">
@@ -1677,11 +1704,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>18800</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="62">
@@ -1692,20 +1719,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="n">
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
         <v>18800</v>
-      </c>
-      <c r="F62" s="8" t="n">
-        <v>21250</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>23670</v>
-      </c>
-      <c r="H62" s="8" t="n">
-        <v>26100</v>
       </c>
     </row>
     <row r="63">
@@ -1716,11 +1734,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="n">
+          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="n">
         <v>18800</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>21250</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>23670</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="64">
@@ -1731,20 +1758,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="n">
-        <v>18150</v>
-      </c>
-      <c r="G64" s="8" t="n">
-        <v>19920</v>
-      </c>
-      <c r="H64" s="8" t="n">
-        <v>21800</v>
-      </c>
-      <c r="I64" s="8" t="n">
-        <v>23550</v>
+          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="65">
@@ -1755,11 +1773,8 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>16300</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
+        </is>
       </c>
       <c r="F65" s="8" t="n">
         <v>18150</v>
@@ -1770,6 +1785,9 @@
       <c r="H65" s="8" t="n">
         <v>21800</v>
       </c>
+      <c r="I65" s="8" t="n">
+        <v>23550</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1779,11 +1797,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>18800</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G66" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>21800</v>
       </c>
     </row>
     <row r="67">
@@ -1794,29 +1821,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mini teatro Fondo del Mar con Títeres de dedo de Animalitos marinos</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>16300</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>18150</v>
-      </c>
-      <c r="F67" s="8" t="n">
-        <v>19920</v>
-      </c>
-      <c r="G67" s="8" t="n">
-        <v>21800</v>
-      </c>
-      <c r="H67" s="8" t="n">
-        <v>23550</v>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>25350</v>
-      </c>
-      <c r="J67" s="8" t="n">
-        <v>27200</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="68">
@@ -1827,11 +1836,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>19980</v>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de Animalitos marinos</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>23550</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>25350</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="69">
@@ -1842,17 +1869,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>14500</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>16200</v>
-      </c>
-      <c r="F69" s="8" t="n">
-        <v>19360</v>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>19980</v>
       </c>
     </row>
     <row r="70">
@@ -1863,23 +1884,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
-        </is>
+          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>14500</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>16300</v>
+        <v>16200</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>18150</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>19920</v>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>21800</v>
-      </c>
-      <c r="I70" s="8" t="n">
-        <v>23550</v>
+        <v>19360</v>
       </c>
     </row>
     <row r="71">
@@ -1890,11 +1905,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="n">
-        <v>19950</v>
+          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="72">
@@ -1905,29 +1932,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>16300</v>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>18150</v>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>19920</v>
-      </c>
-      <c r="H72" s="8" t="n">
-        <v>21800</v>
-      </c>
-      <c r="I72" s="8" t="n">
-        <v>23550</v>
-      </c>
-      <c r="J72" s="8" t="n">
-        <v>25350</v>
-      </c>
-      <c r="K72" s="8" t="n">
-        <v>27200</v>
+          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>19950</v>
       </c>
     </row>
     <row r="73">
@@ -1938,11 +1947,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="n">
-        <v>18200</v>
+          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>23550</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>25350</v>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="74">
@@ -1953,11 +1980,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
+          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>18000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="75">
@@ -1968,23 +1995,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Animalitos del Mar</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>7800</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G75" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H75" s="8" t="n">
-        <v>13200</v>
-      </c>
-      <c r="I75" s="8" t="n">
-        <v>15100</v>
+          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="76">
@@ -1995,7 +2010,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Animalitos domésticos</t>
+          <t>Títeres de dedo de Animalitos del Mar</t>
         </is>
       </c>
       <c r="E76" s="8" t="n">
@@ -2010,6 +2025,9 @@
       <c r="H76" s="8" t="n">
         <v>13200</v>
       </c>
+      <c r="I76" s="8" t="n">
+        <v>15100</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2019,11 +2037,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Caperucita roja</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="n">
+          <t>Títeres de dedo de Animalitos domésticos</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n">
         <v>7800</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="78">
@@ -2034,11 +2061,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>Títeres de dedo de Caperucita roja</t>
         </is>
       </c>
       <c r="C78" s="7" t="n">
-        <v>10300</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="79">
@@ -2049,7 +2076,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento de Hadas</t>
+          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="C79" s="7" t="n">
@@ -2064,7 +2091,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Títeres de dedo de El Circo Mágico</t>
+          <t>Títeres de dedo de Cuento de Hadas</t>
         </is>
       </c>
       <c r="C80" s="7" t="n">
@@ -2079,17 +2106,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Heroínas de cuento</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="n">
+          <t>Títeres de dedo de El Circo Mágico</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n">
         <v>10300</v>
-      </c>
-      <c r="F81" s="8" t="n">
-        <v>12700</v>
-      </c>
-      <c r="H81" s="8" t="n">
-        <v>17600</v>
       </c>
     </row>
     <row r="82">
@@ -2100,20 +2121,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Familia Monte Espino</t>
+          <t>Títeres de dedo de Heroínas de cuento</t>
         </is>
       </c>
       <c r="E82" s="8" t="n">
-        <v>7800</v>
+        <v>10300</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G82" s="8" t="n">
-        <v>11400</v>
+        <v>12700</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>13200</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="83">
@@ -2124,11 +2142,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Prehistoria</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="n">
-        <v>10825</v>
+          <t>Títeres de dedo de La Familia Monte Espino</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="84">
@@ -2139,11 +2166,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Sirenita</t>
+          <t>Títeres de dedo de La Prehistoria</t>
         </is>
       </c>
       <c r="C84" s="7" t="n">
-        <v>11450</v>
+        <v>10825</v>
       </c>
     </row>
     <row r="85">
@@ -2154,20 +2181,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>7800</v>
-      </c>
-      <c r="F85" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G85" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H85" s="8" t="n">
-        <v>13200</v>
+          <t>Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>11450</v>
       </c>
     </row>
     <row r="86">
@@ -2178,11 +2196,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Piratas Siete Mares</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="n">
+          <t>Títeres de dedo de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
         <v>7800</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="87">
@@ -2193,7 +2220,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+          <t>Títeres de dedo de Los Piratas Siete Mares</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
@@ -2208,23 +2235,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Africana</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="n">
+          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
         <v>7800</v>
-      </c>
-      <c r="F88" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G88" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H88" s="8" t="n">
-        <v>13200</v>
-      </c>
-      <c r="I88" s="8" t="n">
-        <v>15100</v>
       </c>
     </row>
     <row r="89">
@@ -2235,7 +2250,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Misionera</t>
+          <t>Títeres de dedo de Selva Africana</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
@@ -2244,6 +2259,15 @@
       <c r="F89" s="8" t="n">
         <v>9600</v>
       </c>
+      <c r="G89" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>15100</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2253,11 +2277,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Superhéroes</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Selva Misionera</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>9600</v>
       </c>
     </row>
     <row r="91">
@@ -2268,23 +2295,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Títeres de dedo de granja</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>7800</v>
-      </c>
-      <c r="F91" s="8" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G91" s="8" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H91" s="8" t="n">
-        <v>13200</v>
-      </c>
-      <c r="I91" s="8" t="n">
-        <v>15100</v>
+          <t>Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="92">
@@ -2295,33 +2310,45 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>Títeres de dedo de granja</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
         </is>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C93" s="7" t="n">
         <v>10300</v>
       </c>
     </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="94" ht="28" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Bolsito Amasando ideas Elefante</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="n">
-        <v>12000</v>
       </c>
     </row>
     <row r="95">
@@ -2332,7 +2359,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Espacio</t>
+          <t>Bolsito Amasando ideas Elefante</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
@@ -2347,7 +2374,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Gato automovilista</t>
+          <t>Bolsito Amasando ideas Espacio</t>
         </is>
       </c>
       <c r="C96" s="7" t="n">
@@ -2362,7 +2389,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Pajaritos</t>
+          <t>Bolsito Amasando ideas Gato automovilista</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
@@ -2377,11 +2404,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+          <t>Bolsito Amasando ideas Pajaritos</t>
         </is>
       </c>
       <c r="C98" s="7" t="n">
-        <v>19500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="99">
@@ -2392,7 +2419,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Haditas</t>
+          <t>Valija de Arte Mini Artista, Dinosaurios</t>
         </is>
       </c>
       <c r="C99" s="7" t="n">
@@ -2407,7 +2434,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Piratas</t>
+          <t>Valija de Arte Mini Artista, Haditas</t>
         </is>
       </c>
       <c r="C100" s="7" t="n">
@@ -2422,7 +2449,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Ponis</t>
+          <t>Valija de Arte Mini Artista, Piratas</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
@@ -2437,7 +2464,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Sirenitas</t>
+          <t>Valija de Arte Mini Artista, Ponis</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
@@ -2452,7 +2479,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Superhéroes</t>
+          <t>Valija de Arte Mini Artista, Sirenitas</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
@@ -2467,11 +2494,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Astronautas</t>
+          <t>Valija de Arte Mini Artista, Superhéroes</t>
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>25850</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="105">
@@ -2482,7 +2509,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
+          <t>Valija de Arte Mis Diseños. Astronautas</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
@@ -2497,7 +2524,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
+          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
@@ -2512,7 +2539,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Monstruos</t>
+          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
@@ -2527,7 +2554,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+          <t>Valija de Arte Mis Diseños. Monstruos</t>
         </is>
       </c>
       <c r="C108" s="7" t="n">
@@ -2542,7 +2569,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
+          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
         </is>
       </c>
       <c r="C109" s="7" t="n">
@@ -2557,7 +2584,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Princesa</t>
+          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
         </is>
       </c>
       <c r="C110" s="7" t="n">
@@ -2572,7 +2599,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Robots</t>
+          <t>Valija de Arte Mis Diseños. Princesa</t>
         </is>
       </c>
       <c r="C111" s="7" t="n">
@@ -2587,33 +2614,33 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Unicornio</t>
+          <t>Valija de Arte Mis Diseños. Robots</t>
         </is>
       </c>
       <c r="C112" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
-    <row r="113" ht="28" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Valija de Arte Mis Diseños. Unicornio</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>25850</v>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Bolsito Chef nena</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="n">
-        <v>11500</v>
       </c>
     </row>
     <row r="115">
@@ -2624,7 +2651,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bolsito Chef varón</t>
+          <t>Bolsito Chef nena</t>
         </is>
       </c>
       <c r="C115" s="7" t="n">
@@ -2639,7 +2666,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bolsito Explorador Jirafas</t>
+          <t>Bolsito Chef varón</t>
         </is>
       </c>
       <c r="C116" s="7" t="n">
@@ -2654,7 +2681,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bolsito Explorador África</t>
+          <t>Bolsito Explorador Jirafas</t>
         </is>
       </c>
       <c r="C117" s="7" t="n">
@@ -2669,7 +2696,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bolsito Mini Peluquería</t>
+          <t>Bolsito Explorador África</t>
         </is>
       </c>
       <c r="C118" s="7" t="n">
@@ -2684,11 +2711,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+          <t>Bolsito Mini Peluquería</t>
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>16500</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="120">
@@ -2699,11 +2726,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef nena</t>
+          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
         </is>
       </c>
       <c r="C120" s="7" t="n">
-        <v>21000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="121">
@@ -2714,7 +2741,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef varón</t>
+          <t>Valija de Mini Chef nena</t>
         </is>
       </c>
       <c r="C121" s="7" t="n">
@@ -2729,11 +2756,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Valija de Mini Doctor</t>
+          <t>Valija de Mini Chef varón</t>
         </is>
       </c>
       <c r="C122" s="7" t="n">
-        <v>37500</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="123">
@@ -2744,11 +2771,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Valija de Mini Exploradores</t>
+          <t>Valija de Mini Doctor</t>
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>24800</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="124">
@@ -2759,11 +2786,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Valija de Mini Jardineros</t>
+          <t>Valija de Mini Exploradores</t>
         </is>
       </c>
       <c r="C124" s="7" t="n">
-        <v>23500</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="125">
@@ -2774,11 +2801,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestra</t>
+          <t>Valija de Mini Jardineros</t>
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>28600</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="126">
@@ -2789,7 +2816,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestro</t>
+          <t>Valija de Mini Maestra</t>
         </is>
       </c>
       <c r="C126" s="7" t="n">
@@ -2804,11 +2831,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Valija de Mini Spa</t>
+          <t>Valija de Mini Maestro</t>
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>29800</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="128">
@@ -2819,11 +2846,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Valija de Mini Veterinarios</t>
+          <t>Valija de Mini Spa</t>
         </is>
       </c>
       <c r="C128" s="7" t="n">
-        <v>26400</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="129">
@@ -2834,11 +2861,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Valija de Tarde de Mate</t>
+          <t>Valija de Mini Veterinarios</t>
         </is>
       </c>
       <c r="C129" s="7" t="n">
-        <v>19500</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="130">
@@ -2849,33 +2876,33 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
+          <t>Valija de Tarde de Mate</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>Valija de Tardes de Té</t>
         </is>
       </c>
-      <c r="C130" s="7" t="n">
+      <c r="C131" s="7" t="n">
         <v>25000</v>
       </c>
     </row>
-    <row r="131" ht="28" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>DISFRACES PARA NENAS</t>
         </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Disfraz de Anna (Frozen)</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="n">
-        <v>24850</v>
       </c>
     </row>
     <row r="133">
@@ -2886,11 +2913,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Disfraz de Bella</t>
+          <t>Disfraz de Anna (Frozen)</t>
         </is>
       </c>
       <c r="C133" s="7" t="n">
-        <v>23970</v>
+        <v>24850</v>
       </c>
     </row>
     <row r="134">
@@ -2901,11 +2928,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Disfraz de Blancanieves</t>
+          <t>Disfraz de Bella</t>
         </is>
       </c>
       <c r="C134" s="7" t="n">
-        <v>24850</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="135">
@@ -2916,11 +2943,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Disfraz de Cenicienta</t>
+          <t>Disfraz de Blancanieves</t>
         </is>
       </c>
       <c r="C135" s="7" t="n">
-        <v>23970</v>
+        <v>24850</v>
       </c>
     </row>
     <row r="136">
@@ -2931,11 +2958,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Disfraz de Elsa (Frozen)</t>
+          <t>Disfraz de Cenicienta</t>
         </is>
       </c>
       <c r="C136" s="7" t="n">
-        <v>24850</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="137">
@@ -2946,11 +2973,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Disfraz de Mira K-Pop Demon Hunters</t>
+          <t>Disfraz de Elsa (Frozen)</t>
         </is>
       </c>
       <c r="C137" s="7" t="n">
-        <v>38500</v>
+        <v>24850</v>
       </c>
     </row>
     <row r="138">
@@ -2961,11 +2988,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Disfraz de Moana</t>
+          <t>Disfraz de Mira K-Pop Demon Hunters</t>
         </is>
       </c>
       <c r="C138" s="7" t="n">
-        <v>24500</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="139">
@@ -2976,11 +3003,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Disfraz de Mujer Maravilla</t>
+          <t>Disfraz de Moana</t>
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>19850</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="140">
@@ -2991,11 +3018,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
+          <t>Disfraz de Mujer Maravilla</t>
         </is>
       </c>
       <c r="C140" s="7" t="n">
-        <v>23970</v>
+        <v>19850</v>
       </c>
     </row>
     <row r="141">
@@ -3006,11 +3033,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Disfraz de Rapunzel Encantada</t>
+          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
         </is>
       </c>
       <c r="C141" s="7" t="n">
-        <v>33300</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="142">
@@ -3021,11 +3048,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
+          <t>Disfraz de Rapunzel Encantada</t>
         </is>
       </c>
       <c r="C142" s="7" t="n">
-        <v>28500</v>
+        <v>33300</v>
       </c>
     </row>
     <row r="143">
@@ -3036,11 +3063,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
+          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>51800</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="144">
@@ -3051,11 +3078,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
+          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
         </is>
       </c>
       <c r="C144" s="7" t="n">
-        <v>53200</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="145">
@@ -3066,11 +3093,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Disfraz de Sirenita</t>
+          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
         </is>
       </c>
       <c r="C145" s="7" t="n">
-        <v>22500</v>
+        <v>53200</v>
       </c>
     </row>
     <row r="146">
@@ -3081,11 +3108,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Disfraz de Unicornio Mágico</t>
+          <t>Disfraz de Sirenita</t>
         </is>
       </c>
       <c r="C146" s="7" t="n">
-        <v>27400</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="147">
@@ -3096,11 +3123,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
+          <t>Disfraz de Unicornio Mágico</t>
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>45000</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="148">
@@ -3111,11 +3138,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tutú de Bailarina Unicornio</t>
+          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
         </is>
       </c>
       <c r="C148" s="7" t="n">
-        <v>23200</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="149">
@@ -3126,33 +3153,33 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
+          <t>Tutú de Bailarina Unicornio</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>23200</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
           <t>Tutú de bailarina</t>
         </is>
       </c>
-      <c r="C149" s="7" t="n">
+      <c r="C150" s="7" t="n">
         <v>19500</v>
       </c>
     </row>
-    <row r="150" ht="28" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>DISFRACES PARA NENES</t>
         </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Disfraz de Batman</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="n">
-        <v>23500</v>
       </c>
     </row>
     <row r="152">
@@ -3163,11 +3190,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Disfraz de Bombero</t>
+          <t>Disfraz de Batman</t>
         </is>
       </c>
       <c r="C152" s="7" t="n">
-        <v>15000</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="153">
@@ -3178,11 +3205,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Disfraz de Capitán América</t>
+          <t>Disfraz de Bombero</t>
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>23500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="154">
@@ -3193,11 +3220,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Disfraz de Hombre Araña</t>
+          <t>Disfraz de Capitán América</t>
         </is>
       </c>
       <c r="C154" s="7" t="n">
-        <v>18000</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="155">
@@ -3208,7 +3235,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Disfraz de Pirata</t>
+          <t>Disfraz de Hombre Araña</t>
         </is>
       </c>
       <c r="C155" s="7" t="n">
@@ -3223,11 +3250,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Disfraz de Policía</t>
+          <t>Disfraz de Pirata</t>
         </is>
       </c>
       <c r="C156" s="7" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="157">
@@ -3238,33 +3265,33 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
+          <t>Disfraz de Policía</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>Disfraz de Superman</t>
         </is>
       </c>
-      <c r="C157" s="7" t="n">
+      <c r="C158" s="7" t="n">
         <v>22000</v>
       </c>
     </row>
-    <row r="158" ht="28" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
+    <row r="159" ht="28" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>DISFRACES DE ANIMALITOS</t>
         </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>DISFRACES DE ANIMALITOS</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Disfraz de Araña</t>
-        </is>
-      </c>
-      <c r="C159" s="7" t="n">
-        <v>23500</v>
       </c>
     </row>
     <row r="160">
@@ -3275,7 +3302,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Disfraz de Cebra</t>
+          <t>Disfraz de Araña</t>
         </is>
       </c>
       <c r="C160" s="7" t="n">
@@ -3290,11 +3317,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Disfraz de Dinosaurio</t>
+          <t>Disfraz de Cebra</t>
         </is>
       </c>
       <c r="C161" s="7" t="n">
-        <v>25200</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="162">
@@ -3305,33 +3332,33 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
+          <t>Disfraz de Dinosaurio</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="n">
+        <v>25200</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
           <t>Disfraz de Tigre</t>
         </is>
       </c>
-      <c r="C162" s="7" t="n">
+      <c r="C163" s="7" t="n">
         <v>23500</v>
       </c>
     </row>
-    <row r="163" ht="28" customHeight="1">
-      <c r="A163" s="6" t="inlineStr">
+    <row r="164" ht="28" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
         <is>
           <t>DISFRACES DE HALLOWEEN</t>
         </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Caramelera Calabaza</t>
-        </is>
-      </c>
-      <c r="C164" s="7" t="n">
-        <v>9000</v>
       </c>
     </row>
     <row r="165">
@@ -3342,11 +3369,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
+          <t>Caramelera Calabaza</t>
         </is>
       </c>
       <c r="C165" s="7" t="n">
-        <v>23500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="166">
@@ -3357,11 +3384,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Fuxia</t>
+          <t>Disfraz de Araña</t>
         </is>
       </c>
       <c r="C166" s="7" t="n">
-        <v>25500</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="167">
@@ -3372,7 +3399,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Naranja</t>
+          <t>Disfraz de Brujita Fuxia</t>
         </is>
       </c>
       <c r="C167" s="7" t="n">
@@ -3387,7 +3414,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Verde</t>
+          <t>Disfraz de Brujita Naranja</t>
         </is>
       </c>
       <c r="C168" s="7" t="n">
@@ -3402,7 +3429,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Violeta</t>
+          <t>Disfraz de Brujita Verde</t>
         </is>
       </c>
       <c r="C169" s="7" t="n">
@@ -3417,11 +3444,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Disfraz de Calabaza</t>
+          <t>Disfraz de Brujita Violeta</t>
         </is>
       </c>
       <c r="C170" s="7" t="n">
-        <v>23500</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="171">
@@ -3432,11 +3459,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Disfraz de Esqueleto</t>
+          <t>Disfraz de Calabaza</t>
         </is>
       </c>
       <c r="C171" s="7" t="n">
-        <v>25000</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="172">
@@ -3447,11 +3474,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Disfraz de Merlina</t>
+          <t>Disfraz de Esqueleto</t>
         </is>
       </c>
       <c r="C172" s="7" t="n">
-        <v>32000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="173">
@@ -3462,33 +3489,33 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
+          <t>Disfraz de Merlina</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
           <t>Disfraz de Vampira</t>
         </is>
       </c>
-      <c r="C173" s="7" t="n">
+      <c r="C174" s="7" t="n">
         <v>25300</v>
       </c>
     </row>
-    <row r="174" ht="28" customHeight="1">
-      <c r="A174" s="6" t="inlineStr">
+    <row r="175" ht="28" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>JUGUETES PARA BEBÉS</t>
         </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Cesto para juguetes Cactus</t>
-        </is>
-      </c>
-      <c r="C175" s="7" t="n">
-        <v>22900</v>
       </c>
     </row>
     <row r="176">
@@ -3499,7 +3526,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cebra y Jirafa</t>
+          <t>Cesto para juguetes Cactus</t>
         </is>
       </c>
       <c r="C176" s="7" t="n">
@@ -3514,7 +3541,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Gatitos</t>
+          <t>Cesto para juguetes Cebra y Jirafa</t>
         </is>
       </c>
       <c r="C177" s="7" t="n">
@@ -3529,7 +3556,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Indi</t>
+          <t>Cesto para juguetes Gatitos</t>
         </is>
       </c>
       <c r="C178" s="7" t="n">
@@ -3544,11 +3571,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Globo Pelota Animalitos</t>
+          <t>Cesto para juguetes Indi</t>
         </is>
       </c>
       <c r="C179" s="7" t="n">
-        <v>6800</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="180">
@@ -3559,7 +3586,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Globo Pelota Dinosaurios</t>
+          <t>Globo Pelota Animalitos</t>
         </is>
       </c>
       <c r="C180" s="7" t="n">
@@ -3574,7 +3601,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Globo Pelota Gatitos</t>
+          <t>Globo Pelota Dinosaurios</t>
         </is>
       </c>
       <c r="C181" s="7" t="n">
@@ -3589,7 +3616,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Globo Pelota Haditas</t>
+          <t>Globo Pelota Gatitos</t>
         </is>
       </c>
       <c r="C182" s="7" t="n">
@@ -3604,7 +3631,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Globo Pelota Monstruos</t>
+          <t>Globo Pelota Haditas</t>
         </is>
       </c>
       <c r="C183" s="7" t="n">
@@ -3619,7 +3646,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Globo Pelota Selva</t>
+          <t>Globo Pelota Monstruos</t>
         </is>
       </c>
       <c r="C184" s="7" t="n">
@@ -3634,11 +3661,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Libro para bebé "Coral"</t>
+          <t>Globo Pelota Selva</t>
         </is>
       </c>
       <c r="C185" s="7" t="n">
-        <v>8400</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="186">
@@ -3649,7 +3676,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Libro para bebé "Cosquillitas"</t>
+          <t>Libro para bebé "Coral"</t>
         </is>
       </c>
       <c r="C186" s="7" t="n">
@@ -3664,7 +3691,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Libro para bebé "Mariposas"</t>
+          <t>Libro para bebé "Cosquillitas"</t>
         </is>
       </c>
       <c r="C187" s="7" t="n">
@@ -3679,11 +3706,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Manta para bebé "Animalitos de la Selva"</t>
+          <t>Libro para bebé "Mariposas"</t>
         </is>
       </c>
       <c r="C188" s="7" t="n">
-        <v>15600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="189">
@@ -3694,7 +3721,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Manta para bebé "La Ciudad"</t>
+          <t>Manta para bebé "Animalitos de la Selva"</t>
         </is>
       </c>
       <c r="C189" s="7" t="n">
@@ -3709,7 +3736,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Manta para bebé "Mininos"</t>
+          <t>Manta para bebé "La Ciudad"</t>
         </is>
       </c>
       <c r="C190" s="7" t="n">
@@ -3724,11 +3751,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Animalitos</t>
+          <t>Manta para bebé "Mininos"</t>
         </is>
       </c>
       <c r="C191" s="7" t="n">
-        <v>15950</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="192">
@@ -3739,7 +3766,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Dinosaurios</t>
+          <t>Pelota de Trapo  Animalitos</t>
         </is>
       </c>
       <c r="C192" s="7" t="n">
@@ -3754,7 +3781,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Gatitos</t>
+          <t>Pelota de Trapo  Dinosaurios</t>
         </is>
       </c>
       <c r="C193" s="7" t="n">
@@ -3769,7 +3796,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Selva</t>
+          <t>Pelota de Trapo Gatitos</t>
         </is>
       </c>
       <c r="C194" s="7" t="n">
@@ -3784,11 +3811,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
+          <t>Pelota de Trapo Selva</t>
         </is>
       </c>
       <c r="C195" s="7" t="n">
-        <v>7500</v>
+        <v>15950</v>
       </c>
     </row>
     <row r="196">
@@ -3799,33 +3826,33 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
+          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
           <t>Rayuela de tela para aprender los números jugando</t>
         </is>
       </c>
-      <c r="C196" s="7" t="n">
+      <c r="C197" s="7" t="n">
         <v>24500</v>
       </c>
     </row>
-    <row r="197" ht="28" customHeight="1">
-      <c r="A197" s="6" t="inlineStr">
+    <row r="198" ht="28" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
         <is>
           <t>MUÑECAS DE TRAPO</t>
         </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Muñeca Piccolina Aurora</t>
-        </is>
-      </c>
-      <c r="C198" s="7" t="n">
-        <v>24350</v>
       </c>
     </row>
     <row r="199">
@@ -3836,7 +3863,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Bella</t>
+          <t>Muñeca Piccolina Aurora</t>
         </is>
       </c>
       <c r="C199" s="7" t="n">
@@ -3851,7 +3878,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Blancanieves</t>
+          <t>Muñeca Piccolina Bella</t>
         </is>
       </c>
       <c r="C200" s="7" t="n">
@@ -3866,7 +3893,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Cenicienta</t>
+          <t>Muñeca Piccolina Blancanieves</t>
         </is>
       </c>
       <c r="C201" s="7" t="n">
@@ -3881,7 +3908,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Coqueta</t>
+          <t>Muñeca Piccolina Cenicienta</t>
         </is>
       </c>
       <c r="C202" s="7" t="n">
@@ -3896,7 +3923,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Deportiva</t>
+          <t>Muñeca Piccolina Coqueta</t>
         </is>
       </c>
       <c r="C203" s="7" t="n">
@@ -3911,7 +3938,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Folk</t>
+          <t>Muñeca Piccolina Deportiva</t>
         </is>
       </c>
       <c r="C204" s="7" t="n">
@@ -3926,7 +3953,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Jardinera</t>
+          <t>Muñeca Piccolina Folk</t>
         </is>
       </c>
       <c r="C205" s="7" t="n">
@@ -3941,7 +3968,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Rapunsel</t>
+          <t>Muñeca Piccolina Jardinera</t>
         </is>
       </c>
       <c r="C206" s="7" t="n">
@@ -3956,7 +3983,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Romántica</t>
+          <t>Muñeca Piccolina Rapunsel</t>
         </is>
       </c>
       <c r="C207" s="7" t="n">
@@ -3971,7 +3998,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Sofía</t>
+          <t>Muñeca Piccolina Romántica</t>
         </is>
       </c>
       <c r="C208" s="7" t="n">
@@ -3986,7 +4013,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina doctora</t>
+          <t>Muñeca Piccolina Sofía</t>
         </is>
       </c>
       <c r="C209" s="7" t="n">
@@ -4001,11 +4028,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Traje de doctora para muñecas</t>
+          <t>Muñeca Piccolina doctora</t>
         </is>
       </c>
       <c r="C210" s="7" t="n">
-        <v>8300</v>
+        <v>24350</v>
       </c>
     </row>
     <row r="211">
@@ -4016,7 +4043,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Traje de jardinera para muñecas</t>
+          <t>Traje de doctora para muñecas</t>
         </is>
       </c>
       <c r="C211" s="7" t="n">
@@ -4031,7 +4058,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Traje deportivo para muñecas</t>
+          <t>Traje de jardinera para muñecas</t>
         </is>
       </c>
       <c r="C212" s="7" t="n">
@@ -4046,7 +4073,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Vestido campesino para muñecas</t>
+          <t>Traje deportivo para muñecas</t>
         </is>
       </c>
       <c r="C213" s="7" t="n">
@@ -4061,7 +4088,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Vestido coqueta para muñecas</t>
+          <t>Vestido campesino para muñecas</t>
         </is>
       </c>
       <c r="C214" s="7" t="n">
@@ -4076,7 +4103,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vestido de Aurora para muñecas</t>
+          <t>Vestido coqueta para muñecas</t>
         </is>
       </c>
       <c r="C215" s="7" t="n">
@@ -4091,7 +4118,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Vestido de Bella para muñecas</t>
+          <t>Vestido de Aurora para muñecas</t>
         </is>
       </c>
       <c r="C216" s="7" t="n">
@@ -4106,7 +4133,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Vestido de Blancanieves para muñecas</t>
+          <t>Vestido de Bella para muñecas</t>
         </is>
       </c>
       <c r="C217" s="7" t="n">
@@ -4121,7 +4148,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Vestido de Cenicienta para muñecas</t>
+          <t>Vestido de Blancanieves para muñecas</t>
         </is>
       </c>
       <c r="C218" s="7" t="n">
@@ -4136,7 +4163,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Vestido de Princesa Sofía para muñecas</t>
+          <t>Vestido de Cenicienta para muñecas</t>
         </is>
       </c>
       <c r="C219" s="7" t="n">
@@ -4151,7 +4178,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Vestido de Rapunzel para muñecas</t>
+          <t>Vestido de Princesa Sofía para muñecas</t>
         </is>
       </c>
       <c r="C220" s="7" t="n">
@@ -4166,29 +4193,44 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
+          <t>Vestido de Rapunzel para muñecas</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
           <t>Vestido romántico para muñecas</t>
         </is>
       </c>
-      <c r="C221" s="7" t="n">
+      <c r="C222" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A174:M174"/>
+    <mergeCell ref="A151:M151"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A150:M150"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A93:M93"/>
-    <mergeCell ref="A158:M158"/>
-    <mergeCell ref="A197:M197"/>
+    <mergeCell ref="A94:M94"/>
+    <mergeCell ref="A132:M132"/>
+    <mergeCell ref="A164:M164"/>
+    <mergeCell ref="A159:M159"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A131:M131"/>
-    <mergeCell ref="A163:M163"/>
-    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A198:M198"/>
+    <mergeCell ref="A56:M56"/>
+    <mergeCell ref="A114:M114"/>
     <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A113:M113"/>
+    <mergeCell ref="A33:M33"/>
+    <mergeCell ref="A175:M175"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
